--- a/artfynd/A 58972-2019 artfynd.xlsx
+++ b/artfynd/A 58972-2019 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123358081</v>
+        <v>123358022</v>
       </c>
       <c r="B2" t="n">
-        <v>58156</v>
+        <v>57497</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,20 +687,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103044</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -708,19 +708,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -734,13 +725,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>345149</v>
+        <v>345132</v>
       </c>
       <c r="R2" t="n">
-        <v>6535556</v>
+        <v>6535541</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -770,6 +761,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Rejäla hackspår i stambasen av en stående grov död gran. I barrskog med gran, tall, björk, asp och ek där det finns flertalet grövre stående döda granar.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -801,10 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123358022</v>
+        <v>123358081</v>
       </c>
       <c r="B3" t="n">
-        <v>57494</v>
+        <v>58159</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,20 +809,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>103044</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -834,10 +830,19 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -851,13 +856,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>345132</v>
+        <v>345149</v>
       </c>
       <c r="R3" t="n">
-        <v>6535541</v>
+        <v>6535556</v>
       </c>
       <c r="S3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -887,11 +892,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-21</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Rejäla hackspår i stambasen av en stående grov död gran. I barrskog med gran, tall, björk, asp och ek där det finns flertalet grövre stående döda granar.</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 58972-2019 artfynd.xlsx
+++ b/artfynd/A 58972-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123358081</v>
       </c>
       <c r="B2" t="n">
-        <v>58159</v>
+        <v>58165</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>123358022</v>
       </c>
       <c r="B3" t="n">
-        <v>57497</v>
+        <v>57503</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 58972-2019 artfynd.xlsx
+++ b/artfynd/A 58972-2019 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123358081</v>
+        <v>123358022</v>
       </c>
       <c r="B2" t="n">
-        <v>58165</v>
+        <v>57506</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,20 +687,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103044</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -708,19 +708,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -734,13 +725,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>345149</v>
+        <v>345132</v>
       </c>
       <c r="R2" t="n">
-        <v>6535556</v>
+        <v>6535541</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -770,6 +761,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Rejäla hackspår i stambasen av en stående grov död gran. I barrskog med gran, tall, björk, asp och ek där det finns flertalet grövre stående döda granar.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -801,10 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123358022</v>
+        <v>123358081</v>
       </c>
       <c r="B3" t="n">
-        <v>57503</v>
+        <v>58168</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,20 +809,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>103044</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -834,10 +830,19 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -851,13 +856,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>345132</v>
+        <v>345149</v>
       </c>
       <c r="R3" t="n">
-        <v>6535541</v>
+        <v>6535556</v>
       </c>
       <c r="S3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -887,11 +892,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-21</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Rejäla hackspår i stambasen av en stående grov död gran. I barrskog med gran, tall, björk, asp och ek där det finns flertalet grövre stående döda granar.</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 58972-2019 artfynd.xlsx
+++ b/artfynd/A 58972-2019 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123358022</v>
+        <v>123358081</v>
       </c>
       <c r="B2" t="n">
-        <v>57506</v>
+        <v>58169</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,20 +687,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>103044</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -708,10 +708,19 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -725,13 +734,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>345132</v>
+        <v>345149</v>
       </c>
       <c r="R2" t="n">
-        <v>6535541</v>
+        <v>6535556</v>
       </c>
       <c r="S2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -761,11 +770,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-03-21</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Rejäla hackspår i stambasen av en stående grov död gran. I barrskog med gran, tall, björk, asp och ek där det finns flertalet grövre stående döda granar.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -797,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123358081</v>
+        <v>123358022</v>
       </c>
       <c r="B3" t="n">
-        <v>58168</v>
+        <v>57507</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -809,20 +813,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103044</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -830,19 +834,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -856,13 +851,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>345149</v>
+        <v>345132</v>
       </c>
       <c r="R3" t="n">
-        <v>6535556</v>
+        <v>6535541</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -892,6 +887,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Rejäla hackspår i stambasen av en stående grov död gran. I barrskog med gran, tall, björk, asp och ek där det finns flertalet grövre stående döda granar.</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 58972-2019 artfynd.xlsx
+++ b/artfynd/A 58972-2019 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123358081</v>
+        <v>123358022</v>
       </c>
       <c r="B2" t="n">
-        <v>58169</v>
+        <v>57507</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,20 +687,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103044</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -708,19 +708,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -734,13 +725,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>345149</v>
+        <v>345132</v>
       </c>
       <c r="R2" t="n">
-        <v>6535556</v>
+        <v>6535541</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -770,6 +761,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Rejäla hackspår i stambasen av en stående grov död gran. I barrskog med gran, tall, björk, asp och ek där det finns flertalet grövre stående döda granar.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -801,10 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123358022</v>
+        <v>123358081</v>
       </c>
       <c r="B3" t="n">
-        <v>57507</v>
+        <v>58169</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,20 +809,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>103044</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -834,10 +830,19 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -851,13 +856,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>345132</v>
+        <v>345149</v>
       </c>
       <c r="R3" t="n">
-        <v>6535541</v>
+        <v>6535556</v>
       </c>
       <c r="S3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -887,11 +892,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-21</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Rejäla hackspår i stambasen av en stående grov död gran. I barrskog med gran, tall, björk, asp och ek där det finns flertalet grövre stående döda granar.</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 58972-2019 artfynd.xlsx
+++ b/artfynd/A 58972-2019 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123358022</v>
+        <v>123358081</v>
       </c>
       <c r="B2" t="n">
-        <v>57507</v>
+        <v>58169</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,20 +687,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>103044</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -708,10 +708,19 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -725,13 +734,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>345132</v>
+        <v>345149</v>
       </c>
       <c r="R2" t="n">
-        <v>6535541</v>
+        <v>6535556</v>
       </c>
       <c r="S2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -761,11 +770,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-03-21</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Rejäla hackspår i stambasen av en stående grov död gran. I barrskog med gran, tall, björk, asp och ek där det finns flertalet grövre stående döda granar.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -797,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123358081</v>
+        <v>123358022</v>
       </c>
       <c r="B3" t="n">
-        <v>58169</v>
+        <v>57507</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -809,20 +813,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103044</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -830,19 +834,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -856,13 +851,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>345149</v>
+        <v>345132</v>
       </c>
       <c r="R3" t="n">
-        <v>6535556</v>
+        <v>6535541</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -892,6 +887,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Rejäla hackspår i stambasen av en stående grov död gran. I barrskog med gran, tall, björk, asp och ek där det finns flertalet grövre stående döda granar.</t>
         </is>
       </c>
       <c r="AD3" t="b">
